--- a/Grading/Grading assignment.xlsx
+++ b/Grading/Grading assignment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trank\Downloads\DSA_GR1_Linked_List\Docs\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trank\Downloads\DSA_GR1_Linked_List\Grading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F504AF-3F0D-4D6C-B3D5-0141619A7087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9BA6FF-5A7F-486F-B22E-64B8D6EB80E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5448" yWindow="1440" windowWidth="14436" windowHeight="9768" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DanhSachSV" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="333">
   <si>
     <t>Học viện Công nghệ Bưu chính Viễn thông – Cơ sở tại TP. Hồ Chí Minh</t>
   </si>
@@ -1031,6 +1031,9 @@
   </si>
   <si>
     <t>Homework</t>
+  </si>
+  <si>
+    <t>P3: Task 2: Missing explanation of pointer order and memory leaks.</t>
   </si>
 </sst>
 </file>
@@ -1387,6 +1390,32 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1394,6 +1423,33 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1423,6 +1479,16 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1441,69 +1507,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1857,40 +1860,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="G1" s="39" t="s">
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="G1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="39"/>
+      <c r="H1" s="52"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="G2" s="39" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="G2" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="39"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -3106,72 +3109,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="23"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="42"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="26"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="45"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="29"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="48"/>
     </row>
     <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -3198,20 +3201,20 @@
       <c r="H4" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="38"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="51"/>
     </row>
     <row r="5" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -3240,20 +3243,20 @@
         <f>SUM(D5:G5)</f>
         <v>7.75</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="20"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="30"/>
     </row>
     <row r="6" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
@@ -3282,20 +3285,20 @@
         <f t="shared" ref="H6:H41" si="1">SUM(D6:G6)</f>
         <v>9.6</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="20"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="30"/>
     </row>
     <row r="7" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
@@ -3324,20 +3327,20 @@
         <f t="shared" si="1"/>
         <v>9.85</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="20"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="30"/>
     </row>
     <row r="8" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
@@ -3350,26 +3353,36 @@
       <c r="C8" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="D8" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2.5</v>
+      </c>
       <c r="H8" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="20"/>
+        <v>9.25</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="30"/>
     </row>
     <row r="9" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
@@ -3398,20 +3411,20 @@
         <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="20"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="30"/>
     </row>
     <row r="10" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
@@ -3440,20 +3453,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="32"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="55"/>
     </row>
     <row r="11" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
@@ -3482,20 +3495,20 @@
         <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="20"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="30"/>
     </row>
     <row r="12" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
@@ -3524,20 +3537,20 @@
         <f t="shared" si="1"/>
         <v>8.25</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="20"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="30"/>
     </row>
     <row r="13" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
@@ -3566,20 +3579,20 @@
         <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="20"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="30"/>
     </row>
     <row r="14" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
@@ -3608,20 +3621,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I14" s="30" t="s">
+      <c r="I14" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="32"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="55"/>
     </row>
     <row r="15" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
@@ -3649,20 +3662,20 @@
       <c r="H15" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I15" s="33" t="s">
+      <c r="I15" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="35"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="58"/>
     </row>
     <row r="16" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
@@ -3691,20 +3704,20 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="20"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="30"/>
     </row>
     <row r="17" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
@@ -3733,20 +3746,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="20"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="30"/>
     </row>
     <row r="18" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
@@ -3775,20 +3788,20 @@
         <f t="shared" si="1"/>
         <v>6.6</v>
       </c>
-      <c r="I18" s="18" t="s">
+      <c r="I18" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="20"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="30"/>
     </row>
     <row r="19" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
@@ -3816,20 +3829,20 @@
       <c r="H19" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I19" s="33" t="s">
+      <c r="I19" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="35"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="58"/>
     </row>
     <row r="20" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
@@ -3857,20 +3870,20 @@
       <c r="H20" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I20" s="33" t="s">
+      <c r="I20" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="35"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+      <c r="T20" s="58"/>
     </row>
     <row r="21" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
@@ -3898,20 +3911,20 @@
       <c r="H21" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I21" s="33" t="s">
+      <c r="I21" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="34"/>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="35"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="58"/>
     </row>
     <row r="22" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
@@ -3940,20 +3953,20 @@
         <f t="shared" si="1"/>
         <v>9.35</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="20"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="30"/>
     </row>
     <row r="23" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
@@ -3981,20 +3994,20 @@
       <c r="H23" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I23" s="33" t="s">
+      <c r="I23" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="35"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="57"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="57"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="58"/>
     </row>
     <row r="24" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
@@ -4023,20 +4036,20 @@
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="I24" s="18" t="s">
+      <c r="I24" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="20"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="30"/>
     </row>
     <row r="25" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
@@ -4065,20 +4078,20 @@
         <f t="shared" si="1"/>
         <v>9.85</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="I25" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="20"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="30"/>
     </row>
     <row r="26" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
@@ -4107,20 +4120,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="30" t="s">
+      <c r="I26" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="32"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
+      <c r="R26" s="54"/>
+      <c r="S26" s="54"/>
+      <c r="T26" s="55"/>
     </row>
     <row r="27" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
@@ -4149,20 +4162,20 @@
         <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="20"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="30"/>
     </row>
     <row r="28" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
@@ -4191,20 +4204,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I28" s="18" t="s">
+      <c r="I28" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="20"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="30"/>
     </row>
     <row r="29" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
@@ -4232,20 +4245,20 @@
       <c r="H29" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I29" s="33" t="s">
+      <c r="I29" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="34"/>
-      <c r="R29" s="34"/>
-      <c r="S29" s="34"/>
-      <c r="T29" s="35"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="57"/>
+      <c r="S29" s="57"/>
+      <c r="T29" s="58"/>
     </row>
     <row r="30" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
@@ -4274,20 +4287,20 @@
         <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
-      <c r="I30" s="18" t="s">
+      <c r="I30" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="20"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="30"/>
     </row>
     <row r="31" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
@@ -4316,20 +4329,20 @@
         <f t="shared" si="1"/>
         <v>7.85</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="I31" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="20"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="30"/>
     </row>
     <row r="32" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
@@ -4358,20 +4371,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="30" t="s">
+      <c r="I32" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="32"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="54"/>
+      <c r="N32" s="54"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="54"/>
+      <c r="R32" s="54"/>
+      <c r="S32" s="54"/>
+      <c r="T32" s="55"/>
     </row>
     <row r="33" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
@@ -4400,20 +4413,20 @@
         <f t="shared" si="1"/>
         <v>8.85</v>
       </c>
-      <c r="I33" s="18" t="s">
+      <c r="I33" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="20"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="30"/>
     </row>
     <row r="34" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
@@ -4442,20 +4455,20 @@
         <f t="shared" si="1"/>
         <v>9.85</v>
       </c>
-      <c r="I34" s="18" t="s">
+      <c r="I34" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="20"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="30"/>
     </row>
     <row r="35" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
@@ -4484,20 +4497,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="30" t="s">
+      <c r="I35" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="31"/>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="32"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="55"/>
     </row>
     <row r="36" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
@@ -4526,20 +4539,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I36" s="18" t="s">
+      <c r="I36" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="20"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="30"/>
     </row>
     <row r="37" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
@@ -4568,20 +4581,20 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I37" s="18" t="s">
+      <c r="I37" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="20"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="30"/>
     </row>
     <row r="38" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
@@ -4610,20 +4623,20 @@
         <f t="shared" si="1"/>
         <v>9.85</v>
       </c>
-      <c r="I38" s="18" t="s">
+      <c r="I38" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
-      <c r="S38" s="19"/>
-      <c r="T38" s="20"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="30"/>
     </row>
     <row r="39" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
@@ -4652,20 +4665,20 @@
         <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
-      <c r="I39" s="18" t="s">
+      <c r="I39" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="20"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="30"/>
     </row>
     <row r="40" spans="1:20" ht="30" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
@@ -4694,20 +4707,20 @@
         <f t="shared" si="1"/>
         <v>9.75</v>
       </c>
-      <c r="I40" s="18" t="s">
+      <c r="I40" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="20"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="30"/>
     </row>
     <row r="41" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
@@ -4736,46 +4749,23 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="I41" s="18" t="s">
+      <c r="I41" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="20"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="I14:T14"/>
-    <mergeCell ref="I4:T4"/>
-    <mergeCell ref="I5:T5"/>
-    <mergeCell ref="I6:T6"/>
-    <mergeCell ref="I7:T7"/>
-    <mergeCell ref="I8:T8"/>
-    <mergeCell ref="I9:T9"/>
-    <mergeCell ref="I10:T10"/>
-    <mergeCell ref="I11:T11"/>
-    <mergeCell ref="I12:T12"/>
-    <mergeCell ref="I13:T13"/>
-    <mergeCell ref="I26:T26"/>
-    <mergeCell ref="I15:T15"/>
-    <mergeCell ref="I16:T16"/>
-    <mergeCell ref="I17:T17"/>
-    <mergeCell ref="I18:T18"/>
-    <mergeCell ref="I19:T19"/>
-    <mergeCell ref="I20:T20"/>
-    <mergeCell ref="I21:T21"/>
-    <mergeCell ref="I22:T22"/>
-    <mergeCell ref="I23:T23"/>
-    <mergeCell ref="I24:T24"/>
-    <mergeCell ref="I25:T25"/>
     <mergeCell ref="I39:T39"/>
     <mergeCell ref="I40:T40"/>
     <mergeCell ref="I41:T41"/>
@@ -4792,6 +4782,29 @@
     <mergeCell ref="I30:T30"/>
     <mergeCell ref="I31:T31"/>
     <mergeCell ref="I32:T32"/>
+    <mergeCell ref="I26:T26"/>
+    <mergeCell ref="I15:T15"/>
+    <mergeCell ref="I16:T16"/>
+    <mergeCell ref="I17:T17"/>
+    <mergeCell ref="I18:T18"/>
+    <mergeCell ref="I19:T19"/>
+    <mergeCell ref="I20:T20"/>
+    <mergeCell ref="I21:T21"/>
+    <mergeCell ref="I22:T22"/>
+    <mergeCell ref="I23:T23"/>
+    <mergeCell ref="I24:T24"/>
+    <mergeCell ref="I25:T25"/>
+    <mergeCell ref="I14:T14"/>
+    <mergeCell ref="I4:T4"/>
+    <mergeCell ref="I5:T5"/>
+    <mergeCell ref="I6:T6"/>
+    <mergeCell ref="I7:T7"/>
+    <mergeCell ref="I8:T8"/>
+    <mergeCell ref="I9:T9"/>
+    <mergeCell ref="I10:T10"/>
+    <mergeCell ref="I11:T11"/>
+    <mergeCell ref="I12:T12"/>
+    <mergeCell ref="I13:T13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4812,75 +4825,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="40" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="23"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="42"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="26"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="45"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="29"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="48"/>
     </row>
     <row r="4" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -4910,27 +4923,27 @@
       <c r="I4" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="38"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="51"/>
     </row>
     <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <f>ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="18" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -4955,25 +4968,25 @@
         <f>SUM(D5:H5)</f>
         <v>10</v>
       </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="20"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="30"/>
     </row>
     <row r="6" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <f t="shared" ref="A6:A41" si="0">ROW()-4</f>
         <v>2</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="18" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="8" t="s">
@@ -4998,27 +5011,27 @@
         <f t="shared" ref="I6:I41" si="1">SUM(D6:H6)</f>
         <v>9</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="20"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="30"/>
     </row>
     <row r="7" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="18" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -5043,27 +5056,27 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="20"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="30"/>
     </row>
     <row r="8" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="18" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="8" t="s">
@@ -5078,25 +5091,25 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="18"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="20"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="30"/>
     </row>
     <row r="9" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -5121,72 +5134,72 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="28" t="s">
         <v>327</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="20"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="30"/>
     </row>
     <row r="10" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="18" t="s">
         <v>57</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="19">
         <v>1</v>
       </c>
-      <c r="E10" s="41">
-        <v>2.5</v>
-      </c>
-      <c r="F10" s="41">
+      <c r="E10" s="19">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="19">
         <v>2</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="19">
         <v>1.5</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="19">
         <v>2</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J10" s="42" t="s">
+      <c r="J10" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="44"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="33"/>
     </row>
     <row r="11" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="18" t="s">
         <v>62</v>
       </c>
       <c r="C11" s="8" t="s">
@@ -5211,70 +5224,70 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="20"/>
-    </row>
-    <row r="12" spans="1:21" s="51" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="45">
+      <c r="J11" s="28"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="30"/>
+    </row>
+    <row r="12" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="D12" s="45">
-        <v>0</v>
-      </c>
-      <c r="E12" s="45">
-        <v>0</v>
-      </c>
-      <c r="F12" s="45">
-        <v>0</v>
-      </c>
-      <c r="G12" s="45">
-        <v>0</v>
-      </c>
-      <c r="H12" s="45">
-        <v>0</v>
-      </c>
-      <c r="I12" s="45">
+      <c r="D12" s="20">
+        <v>0</v>
+      </c>
+      <c r="E12" s="20">
+        <v>0</v>
+      </c>
+      <c r="F12" s="20">
+        <v>0</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0</v>
+      </c>
+      <c r="H12" s="20">
+        <v>0</v>
+      </c>
+      <c r="I12" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="48" t="s">
+      <c r="J12" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="50"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="36"/>
     </row>
     <row r="13" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="18" t="s">
         <v>74</v>
       </c>
       <c r="C13" s="8" t="s">
@@ -5299,115 +5312,115 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J13" s="18"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="20"/>
-    </row>
-    <row r="14" spans="1:21" s="51" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A14" s="45">
+      <c r="J13" s="28"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="30"/>
+    </row>
+    <row r="14" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="20">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="D14" s="45">
-        <v>0</v>
-      </c>
-      <c r="E14" s="45">
-        <v>0</v>
-      </c>
-      <c r="F14" s="45">
-        <v>0</v>
-      </c>
-      <c r="G14" s="45">
-        <v>0</v>
-      </c>
-      <c r="H14" s="45">
-        <v>0</v>
-      </c>
-      <c r="I14" s="45">
+      <c r="D14" s="20">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
+        <v>0</v>
+      </c>
+      <c r="G14" s="20">
+        <v>0</v>
+      </c>
+      <c r="H14" s="20">
+        <v>0</v>
+      </c>
+      <c r="I14" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="48" t="s">
+      <c r="J14" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
-      <c r="N14" s="49"/>
-      <c r="O14" s="49"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="49"/>
-      <c r="S14" s="49"/>
-      <c r="T14" s="49"/>
-      <c r="U14" s="50"/>
-    </row>
-    <row r="15" spans="1:21" s="58" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="52">
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="36"/>
+    </row>
+    <row r="15" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="F15" s="52" t="s">
+      <c r="F15" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="G15" s="52" t="s">
+      <c r="G15" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="55" t="s">
+      <c r="J15" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="K15" s="56"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="56"/>
-      <c r="N15" s="56"/>
-      <c r="O15" s="56"/>
-      <c r="P15" s="56"/>
-      <c r="Q15" s="56"/>
-      <c r="R15" s="56"/>
-      <c r="S15" s="56"/>
-      <c r="T15" s="56"/>
-      <c r="U15" s="57"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="39"/>
     </row>
     <row r="16" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="18" t="s">
         <v>92</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -5432,25 +5445,25 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="20"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="30"/>
     </row>
     <row r="17" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="18" t="s">
         <v>98</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -5475,25 +5488,25 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J17" s="18"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="20"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="30"/>
     </row>
     <row r="18" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="18" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -5518,250 +5531,250 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J18" s="18"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="20"/>
-    </row>
-    <row r="19" spans="1:21" s="58" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A19" s="52">
+      <c r="J18" s="28"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="30"/>
+    </row>
+    <row r="19" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="D19" s="52" t="s">
+      <c r="D19" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="E19" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="F19" s="52" t="s">
+      <c r="F19" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="G19" s="52" t="s">
+      <c r="G19" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="55" t="s">
+      <c r="J19" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="K19" s="56"/>
-      <c r="L19" s="56"/>
-      <c r="M19" s="56"/>
-      <c r="N19" s="56"/>
-      <c r="O19" s="56"/>
-      <c r="P19" s="56"/>
-      <c r="Q19" s="56"/>
-      <c r="R19" s="56"/>
-      <c r="S19" s="56"/>
-      <c r="T19" s="56"/>
-      <c r="U19" s="57"/>
-    </row>
-    <row r="20" spans="1:21" s="58" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A20" s="52">
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="39"/>
+    </row>
+    <row r="20" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="24">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="G20" s="52" t="s">
+      <c r="G20" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="I20" s="52">
+      <c r="I20" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="55" t="s">
+      <c r="J20" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="K20" s="56"/>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="56"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="56"/>
-      <c r="R20" s="56"/>
-      <c r="S20" s="56"/>
-      <c r="T20" s="56"/>
-      <c r="U20" s="57"/>
-    </row>
-    <row r="21" spans="1:21" s="58" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A21" s="52">
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="39"/>
+    </row>
+    <row r="21" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="24">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="D21" s="52" t="s">
+      <c r="D21" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E21" s="52" t="s">
+      <c r="E21" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="F21" s="52" t="s">
+      <c r="F21" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="G21" s="52" t="s">
+      <c r="G21" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H21" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="I21" s="52">
+      <c r="I21" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="55" t="s">
+      <c r="J21" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="K21" s="56"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="56"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="56"/>
-      <c r="R21" s="56"/>
-      <c r="S21" s="56"/>
-      <c r="T21" s="56"/>
-      <c r="U21" s="57"/>
-    </row>
-    <row r="22" spans="1:21" s="51" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A22" s="45">
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="39"/>
+    </row>
+    <row r="22" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="D22" s="45">
-        <v>0</v>
-      </c>
-      <c r="E22" s="45">
-        <v>0</v>
-      </c>
-      <c r="F22" s="45">
-        <v>0</v>
-      </c>
-      <c r="G22" s="45">
-        <v>0</v>
-      </c>
-      <c r="H22" s="45">
-        <v>0</v>
-      </c>
-      <c r="I22" s="45">
+      <c r="D22" s="20">
+        <v>0</v>
+      </c>
+      <c r="E22" s="20">
+        <v>0</v>
+      </c>
+      <c r="F22" s="20">
+        <v>0</v>
+      </c>
+      <c r="G22" s="20">
+        <v>0</v>
+      </c>
+      <c r="H22" s="20">
+        <v>0</v>
+      </c>
+      <c r="I22" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="48" t="s">
+      <c r="J22" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="49"/>
-      <c r="P22" s="49"/>
-      <c r="Q22" s="49"/>
-      <c r="R22" s="49"/>
-      <c r="S22" s="49"/>
-      <c r="T22" s="49"/>
-      <c r="U22" s="50"/>
-    </row>
-    <row r="23" spans="1:21" s="58" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A23" s="52">
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="36"/>
+    </row>
+    <row r="23" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="24">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="54" t="s">
+      <c r="C23" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E23" s="52" t="s">
+      <c r="E23" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="F23" s="52" t="s">
+      <c r="F23" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="G23" s="52" t="s">
+      <c r="G23" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="H23" s="52" t="s">
+      <c r="H23" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="I23" s="52">
+      <c r="I23" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="55" t="s">
+      <c r="J23" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="K23" s="56"/>
-      <c r="L23" s="56"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="56"/>
-      <c r="O23" s="56"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="56"/>
-      <c r="R23" s="56"/>
-      <c r="S23" s="56"/>
-      <c r="T23" s="56"/>
-      <c r="U23" s="57"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="39"/>
     </row>
     <row r="24" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="18" t="s">
         <v>139</v>
       </c>
       <c r="C24" s="8" t="s">
@@ -5786,27 +5799,27 @@
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="J24" s="18" t="s">
+      <c r="J24" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="20"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="30"/>
     </row>
     <row r="25" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="18" t="s">
         <v>145</v>
       </c>
       <c r="C25" s="8" t="s">
@@ -5831,72 +5844,72 @@
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
-      <c r="J25" s="18" t="s">
+      <c r="J25" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="20"/>
-    </row>
-    <row r="26" spans="1:21" s="51" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A26" s="45">
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="30"/>
+    </row>
+    <row r="26" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A26" s="20">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="D26" s="45">
-        <v>0</v>
-      </c>
-      <c r="E26" s="45">
-        <v>0</v>
-      </c>
-      <c r="F26" s="45">
-        <v>0</v>
-      </c>
-      <c r="G26" s="45">
-        <v>0</v>
-      </c>
-      <c r="H26" s="45">
-        <v>0</v>
-      </c>
-      <c r="I26" s="45">
+      <c r="D26" s="20">
+        <v>0</v>
+      </c>
+      <c r="E26" s="20">
+        <v>0</v>
+      </c>
+      <c r="F26" s="20">
+        <v>0</v>
+      </c>
+      <c r="G26" s="20">
+        <v>0</v>
+      </c>
+      <c r="H26" s="20">
+        <v>0</v>
+      </c>
+      <c r="I26" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J26" s="48" t="s">
+      <c r="J26" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="K26" s="49"/>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="50"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="36"/>
     </row>
     <row r="27" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="18" t="s">
         <v>157</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -5921,25 +5934,25 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J27" s="18"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="20"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="30"/>
     </row>
     <row r="28" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <f>ROW()-4</f>
         <v>24</v>
       </c>
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="18" t="s">
         <v>163</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -5964,76 +5977,76 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J28" s="18"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="20"/>
-    </row>
-    <row r="29" spans="1:21" s="58" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A29" s="52">
+      <c r="J28" s="28"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="30"/>
+    </row>
+    <row r="29" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A29" s="24">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B29" s="53" t="s">
+      <c r="B29" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="C29" s="54" t="s">
+      <c r="C29" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="F29" s="52" t="s">
+      <c r="F29" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="G29" s="52" t="s">
+      <c r="G29" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="H29" s="52" t="s">
+      <c r="H29" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="I29" s="52">
+      <c r="I29" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="55" t="s">
+      <c r="J29" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="K29" s="56"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="56"/>
-      <c r="P29" s="56"/>
-      <c r="Q29" s="56"/>
-      <c r="R29" s="56"/>
-      <c r="S29" s="56"/>
-      <c r="T29" s="56"/>
-      <c r="U29" s="57"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="38"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="39"/>
     </row>
     <row r="30" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="18" t="s">
         <v>174</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="19">
         <v>0.75</v>
       </c>
       <c r="E30" s="5">
@@ -6052,122 +6065,122 @@
         <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
-      <c r="J30" s="18" t="s">
+      <c r="J30" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="20"/>
-    </row>
-    <row r="31" spans="1:21" s="51" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A31" s="45">
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="30"/>
+    </row>
+    <row r="31" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A31" s="20">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="D31" s="45">
-        <v>0</v>
-      </c>
-      <c r="E31" s="45">
-        <v>0</v>
-      </c>
-      <c r="F31" s="45">
-        <v>0</v>
-      </c>
-      <c r="G31" s="45">
-        <v>0</v>
-      </c>
-      <c r="H31" s="45">
-        <v>0</v>
-      </c>
-      <c r="I31" s="45">
+      <c r="D31" s="20">
+        <v>0</v>
+      </c>
+      <c r="E31" s="20">
+        <v>0</v>
+      </c>
+      <c r="F31" s="20">
+        <v>0</v>
+      </c>
+      <c r="G31" s="20">
+        <v>0</v>
+      </c>
+      <c r="H31" s="20">
+        <v>0</v>
+      </c>
+      <c r="I31" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="48" t="s">
+      <c r="J31" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="49"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="49"/>
-      <c r="R31" s="49"/>
-      <c r="S31" s="49"/>
-      <c r="T31" s="49"/>
-      <c r="U31" s="50"/>
-    </row>
-    <row r="32" spans="1:21" s="51" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A32" s="45">
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="36"/>
+    </row>
+    <row r="32" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A32" s="20">
         <f>ROW()-4</f>
         <v>28</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="D32" s="45">
-        <v>0</v>
-      </c>
-      <c r="E32" s="45">
-        <v>0</v>
-      </c>
-      <c r="F32" s="45">
-        <v>0</v>
-      </c>
-      <c r="G32" s="45">
-        <v>0</v>
-      </c>
-      <c r="H32" s="45">
-        <v>0</v>
-      </c>
-      <c r="I32" s="45">
-        <v>0</v>
-      </c>
-      <c r="J32" s="48" t="s">
+      <c r="D32" s="20">
+        <v>0</v>
+      </c>
+      <c r="E32" s="20">
+        <v>0</v>
+      </c>
+      <c r="F32" s="20">
+        <v>0</v>
+      </c>
+      <c r="G32" s="20">
+        <v>0</v>
+      </c>
+      <c r="H32" s="20">
+        <v>0</v>
+      </c>
+      <c r="I32" s="20">
+        <v>0</v>
+      </c>
+      <c r="J32" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="49"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="49"/>
-      <c r="P32" s="49"/>
-      <c r="Q32" s="49"/>
-      <c r="R32" s="49"/>
-      <c r="S32" s="49"/>
-      <c r="T32" s="49"/>
-      <c r="U32" s="50"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35"/>
+      <c r="U32" s="36"/>
     </row>
     <row r="33" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="18" t="s">
         <v>194</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="19">
         <v>1</v>
       </c>
       <c r="E33" s="5">
@@ -6186,27 +6199,27 @@
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="J33" s="42" t="s">
+      <c r="J33" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="K33" s="43"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="43"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="44"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="33"/>
     </row>
     <row r="34" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="18" t="s">
         <v>198</v>
       </c>
       <c r="C34" s="8" t="s">
@@ -6231,70 +6244,70 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J34" s="18"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="20"/>
-    </row>
-    <row r="35" spans="1:21" s="51" customFormat="1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A35" s="45">
+      <c r="J34" s="28"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="30"/>
+    </row>
+    <row r="35" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A35" s="20">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B35" s="46" t="s">
+      <c r="B35" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="D35" s="45">
-        <v>0</v>
-      </c>
-      <c r="E35" s="45">
-        <v>0</v>
-      </c>
-      <c r="F35" s="45">
-        <v>0</v>
-      </c>
-      <c r="G35" s="45">
-        <v>0</v>
-      </c>
-      <c r="H35" s="45">
-        <v>0</v>
-      </c>
-      <c r="I35" s="45">
+      <c r="D35" s="20">
+        <v>0</v>
+      </c>
+      <c r="E35" s="20">
+        <v>0</v>
+      </c>
+      <c r="F35" s="20">
+        <v>0</v>
+      </c>
+      <c r="G35" s="20">
+        <v>0</v>
+      </c>
+      <c r="H35" s="20">
+        <v>0</v>
+      </c>
+      <c r="I35" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J35" s="48" t="s">
+      <c r="J35" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="49"/>
-      <c r="P35" s="49"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="49"/>
-      <c r="S35" s="49"/>
-      <c r="T35" s="49"/>
-      <c r="U35" s="50"/>
-    </row>
-    <row r="36" spans="1:21" ht="30" x14ac:dyDescent="0.3">
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="36"/>
+    </row>
+    <row r="36" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <f>ROW()-4</f>
         <v>32</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B36" s="18" t="s">
         <v>210</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -6319,72 +6332,72 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J36" s="18" t="s">
+      <c r="J36" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="20"/>
-    </row>
-    <row r="37" spans="1:21" s="51" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A37" s="45">
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="30"/>
+    </row>
+    <row r="37" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A37" s="20">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B37" s="46" t="s">
+      <c r="B37" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="C37" s="47" t="s">
+      <c r="C37" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="D37" s="45">
-        <v>0</v>
-      </c>
-      <c r="E37" s="45">
-        <v>0</v>
-      </c>
-      <c r="F37" s="45">
-        <v>0</v>
-      </c>
-      <c r="G37" s="45">
-        <v>0</v>
-      </c>
-      <c r="H37" s="45">
-        <v>0</v>
-      </c>
-      <c r="I37" s="45">
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="20">
+        <v>0</v>
+      </c>
+      <c r="F37" s="20">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
+        <v>0</v>
+      </c>
+      <c r="H37" s="20">
+        <v>0</v>
+      </c>
+      <c r="I37" s="20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J37" s="48" t="s">
+      <c r="J37" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="49"/>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49"/>
-      <c r="U37" s="50"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="35"/>
+      <c r="T37" s="35"/>
+      <c r="U37" s="36"/>
     </row>
     <row r="38" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="18" t="s">
         <v>221</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -6409,27 +6422,27 @@
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
-      <c r="J38" s="18" t="s">
+      <c r="J38" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
-      <c r="S38" s="19"/>
-      <c r="T38" s="19"/>
-      <c r="U38" s="20"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="30"/>
     </row>
     <row r="39" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <f>ROW()-4</f>
         <v>35</v>
       </c>
-      <c r="B39" s="40" t="s">
+      <c r="B39" s="18" t="s">
         <v>226</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -6454,27 +6467,27 @@
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="J39" s="18" t="s">
+      <c r="J39" s="28" t="s">
         <v>326</v>
       </c>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="20"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="30"/>
     </row>
     <row r="40" spans="1:21" ht="30" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="18" t="s">
         <v>232</v>
       </c>
       <c r="C40" s="8" t="s">
@@ -6499,27 +6512,27 @@
         <f t="shared" si="1"/>
         <v>5.5</v>
       </c>
-      <c r="J40" s="18" t="s">
+      <c r="J40" s="28" t="s">
         <v>328</v>
       </c>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="20"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="30"/>
     </row>
     <row r="41" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="18" t="s">
         <v>238</v>
       </c>
       <c r="C41" s="8" t="s">
@@ -6544,21 +6557,51 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J41" s="18"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="20"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
+      <c r="U41" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="J8:U8"/>
+    <mergeCell ref="A1:U3"/>
+    <mergeCell ref="J4:U4"/>
+    <mergeCell ref="J5:U5"/>
+    <mergeCell ref="J6:U6"/>
+    <mergeCell ref="J7:U7"/>
+    <mergeCell ref="J20:U20"/>
+    <mergeCell ref="J9:U9"/>
+    <mergeCell ref="J10:U10"/>
+    <mergeCell ref="J11:U11"/>
+    <mergeCell ref="J12:U12"/>
+    <mergeCell ref="J13:U13"/>
+    <mergeCell ref="J14:U14"/>
+    <mergeCell ref="J15:U15"/>
+    <mergeCell ref="J16:U16"/>
+    <mergeCell ref="J17:U17"/>
+    <mergeCell ref="J18:U18"/>
+    <mergeCell ref="J19:U19"/>
+    <mergeCell ref="J32:U32"/>
+    <mergeCell ref="J21:U21"/>
+    <mergeCell ref="J22:U22"/>
+    <mergeCell ref="J23:U23"/>
+    <mergeCell ref="J24:U24"/>
+    <mergeCell ref="J25:U25"/>
+    <mergeCell ref="J26:U26"/>
+    <mergeCell ref="J27:U27"/>
+    <mergeCell ref="J28:U28"/>
+    <mergeCell ref="J29:U29"/>
+    <mergeCell ref="J30:U30"/>
+    <mergeCell ref="J31:U31"/>
     <mergeCell ref="J39:U39"/>
     <mergeCell ref="J40:U40"/>
     <mergeCell ref="J41:U41"/>
@@ -6568,36 +6611,6 @@
     <mergeCell ref="J36:U36"/>
     <mergeCell ref="J37:U37"/>
     <mergeCell ref="J38:U38"/>
-    <mergeCell ref="J27:U27"/>
-    <mergeCell ref="J28:U28"/>
-    <mergeCell ref="J29:U29"/>
-    <mergeCell ref="J30:U30"/>
-    <mergeCell ref="J31:U31"/>
-    <mergeCell ref="J32:U32"/>
-    <mergeCell ref="J21:U21"/>
-    <mergeCell ref="J22:U22"/>
-    <mergeCell ref="J23:U23"/>
-    <mergeCell ref="J24:U24"/>
-    <mergeCell ref="J25:U25"/>
-    <mergeCell ref="J26:U26"/>
-    <mergeCell ref="J15:U15"/>
-    <mergeCell ref="J16:U16"/>
-    <mergeCell ref="J17:U17"/>
-    <mergeCell ref="J18:U18"/>
-    <mergeCell ref="J19:U19"/>
-    <mergeCell ref="J20:U20"/>
-    <mergeCell ref="J9:U9"/>
-    <mergeCell ref="J10:U10"/>
-    <mergeCell ref="J11:U11"/>
-    <mergeCell ref="J12:U12"/>
-    <mergeCell ref="J13:U13"/>
-    <mergeCell ref="J14:U14"/>
-    <mergeCell ref="A1:U3"/>
-    <mergeCell ref="J4:U4"/>
-    <mergeCell ref="J5:U5"/>
-    <mergeCell ref="J6:U6"/>
-    <mergeCell ref="J7:U7"/>
-    <mergeCell ref="J8:U8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Grading/Grading assignment.xlsx
+++ b/Grading/Grading assignment.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9BA6FF-5A7F-486F-B22E-64B8D6EB80E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5448" yWindow="1440" windowWidth="14436" windowHeight="9768" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5448" yWindow="1440" windowWidth="14436" windowHeight="9768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DanhSachSV" sheetId="1" r:id="rId1"/>
@@ -1425,33 +1425,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1479,16 +1452,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1505,6 +1468,43 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1860,40 +1860,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="G1" s="52" t="s">
+      <c r="A1" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="G1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="52"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="G2" s="52" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="G2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="52"/>
+      <c r="H2" s="49"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -3109,72 +3109,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="42"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="33"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="45"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="36"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="48"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="39"/>
     </row>
     <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -3201,20 +3201,20 @@
       <c r="H4" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="I4" s="46" t="s">
         <v>251</v>
       </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="51"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="48"/>
     </row>
     <row r="5" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -3453,20 +3453,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I10" s="53" t="s">
+      <c r="I10" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="55"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="42"/>
     </row>
     <row r="11" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
@@ -3621,20 +3621,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I14" s="53" t="s">
+      <c r="I14" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="55"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="41"/>
+      <c r="T14" s="42"/>
     </row>
     <row r="15" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
@@ -3662,20 +3662,20 @@
       <c r="H15" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I15" s="56" t="s">
+      <c r="I15" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="57"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="57"/>
-      <c r="P15" s="57"/>
-      <c r="Q15" s="57"/>
-      <c r="R15" s="57"/>
-      <c r="S15" s="57"/>
-      <c r="T15" s="58"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="45"/>
     </row>
     <row r="16" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
@@ -3829,20 +3829,20 @@
       <c r="H19" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I19" s="56" t="s">
+      <c r="I19" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="57"/>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-      <c r="T19" s="58"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="44"/>
+      <c r="S19" s="44"/>
+      <c r="T19" s="45"/>
     </row>
     <row r="20" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
@@ -3870,20 +3870,20 @@
       <c r="H20" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I20" s="56" t="s">
+      <c r="I20" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="57"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="57"/>
-      <c r="R20" s="57"/>
-      <c r="S20" s="57"/>
-      <c r="T20" s="58"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="44"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="44"/>
+      <c r="R20" s="44"/>
+      <c r="S20" s="44"/>
+      <c r="T20" s="45"/>
     </row>
     <row r="21" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
@@ -3911,20 +3911,20 @@
       <c r="H21" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I21" s="56" t="s">
+      <c r="I21" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="57"/>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="57"/>
-      <c r="R21" s="57"/>
-      <c r="S21" s="57"/>
-      <c r="T21" s="58"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="45"/>
     </row>
     <row r="22" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
@@ -3994,20 +3994,20 @@
       <c r="H23" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I23" s="56" t="s">
+      <c r="I23" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="57"/>
-      <c r="P23" s="57"/>
-      <c r="Q23" s="57"/>
-      <c r="R23" s="57"/>
-      <c r="S23" s="57"/>
-      <c r="T23" s="58"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="44"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="45"/>
     </row>
     <row r="24" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
@@ -4120,20 +4120,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="53" t="s">
+      <c r="I26" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
-      <c r="R26" s="54"/>
-      <c r="S26" s="54"/>
-      <c r="T26" s="55"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="41"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="42"/>
     </row>
     <row r="27" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
@@ -4245,20 +4245,20 @@
       <c r="H29" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I29" s="56" t="s">
+      <c r="I29" s="43" t="s">
         <v>293</v>
       </c>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="57"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="57"/>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="57"/>
-      <c r="R29" s="57"/>
-      <c r="S29" s="57"/>
-      <c r="T29" s="58"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="45"/>
     </row>
     <row r="30" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
@@ -4371,20 +4371,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="53" t="s">
+      <c r="I32" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="54"/>
-      <c r="M32" s="54"/>
-      <c r="N32" s="54"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="54"/>
-      <c r="Q32" s="54"/>
-      <c r="R32" s="54"/>
-      <c r="S32" s="54"/>
-      <c r="T32" s="55"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="41"/>
+      <c r="L32" s="41"/>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="42"/>
     </row>
     <row r="33" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
@@ -4497,20 +4497,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="53" t="s">
+      <c r="I35" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="J35" s="54"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="54"/>
-      <c r="N35" s="54"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="55"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="41"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="42"/>
     </row>
     <row r="36" spans="1:20" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
@@ -4766,6 +4766,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="I14:T14"/>
+    <mergeCell ref="I4:T4"/>
+    <mergeCell ref="I5:T5"/>
+    <mergeCell ref="I6:T6"/>
+    <mergeCell ref="I7:T7"/>
+    <mergeCell ref="I8:T8"/>
+    <mergeCell ref="I9:T9"/>
+    <mergeCell ref="I10:T10"/>
+    <mergeCell ref="I11:T11"/>
+    <mergeCell ref="I12:T12"/>
+    <mergeCell ref="I13:T13"/>
+    <mergeCell ref="I26:T26"/>
+    <mergeCell ref="I15:T15"/>
+    <mergeCell ref="I16:T16"/>
+    <mergeCell ref="I17:T17"/>
+    <mergeCell ref="I18:T18"/>
+    <mergeCell ref="I19:T19"/>
+    <mergeCell ref="I20:T20"/>
+    <mergeCell ref="I21:T21"/>
+    <mergeCell ref="I22:T22"/>
+    <mergeCell ref="I23:T23"/>
+    <mergeCell ref="I24:T24"/>
+    <mergeCell ref="I25:T25"/>
     <mergeCell ref="I39:T39"/>
     <mergeCell ref="I40:T40"/>
     <mergeCell ref="I41:T41"/>
@@ -4782,29 +4805,6 @@
     <mergeCell ref="I30:T30"/>
     <mergeCell ref="I31:T31"/>
     <mergeCell ref="I32:T32"/>
-    <mergeCell ref="I26:T26"/>
-    <mergeCell ref="I15:T15"/>
-    <mergeCell ref="I16:T16"/>
-    <mergeCell ref="I17:T17"/>
-    <mergeCell ref="I18:T18"/>
-    <mergeCell ref="I19:T19"/>
-    <mergeCell ref="I20:T20"/>
-    <mergeCell ref="I21:T21"/>
-    <mergeCell ref="I22:T22"/>
-    <mergeCell ref="I23:T23"/>
-    <mergeCell ref="I24:T24"/>
-    <mergeCell ref="I25:T25"/>
-    <mergeCell ref="I14:T14"/>
-    <mergeCell ref="I4:T4"/>
-    <mergeCell ref="I5:T5"/>
-    <mergeCell ref="I6:T6"/>
-    <mergeCell ref="I7:T7"/>
-    <mergeCell ref="I8:T8"/>
-    <mergeCell ref="I9:T9"/>
-    <mergeCell ref="I10:T10"/>
-    <mergeCell ref="I11:T11"/>
-    <mergeCell ref="I12:T12"/>
-    <mergeCell ref="I13:T13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4825,75 +4825,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="31" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="42"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="33"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="45"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="36"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="48"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="39"/>
     </row>
     <row r="4" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -4923,20 +4923,20 @@
       <c r="I4" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="J4" s="49" t="s">
+      <c r="J4" s="46" t="s">
         <v>251</v>
       </c>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="51"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="48"/>
     </row>
     <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -5179,20 +5179,20 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="53" t="s">
         <v>318</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="33"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="55"/>
     </row>
     <row r="11" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
@@ -5267,20 +5267,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="34" t="s">
+      <c r="J12" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35"/>
-      <c r="U12" s="36"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
+      <c r="P12" s="57"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="57"/>
+      <c r="S12" s="57"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="58"/>
     </row>
     <row r="13" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
@@ -5355,20 +5355,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="34" t="s">
+      <c r="J14" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="36"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="58"/>
     </row>
     <row r="15" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="24">
@@ -5400,20 +5400,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="37" t="s">
+      <c r="J15" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="38"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="39"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="51"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="51"/>
+      <c r="S15" s="51"/>
+      <c r="T15" s="51"/>
+      <c r="U15" s="52"/>
     </row>
     <row r="16" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
@@ -5574,20 +5574,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="37" t="s">
+      <c r="J19" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="38"/>
-      <c r="S19" s="38"/>
-      <c r="T19" s="38"/>
-      <c r="U19" s="39"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="51"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="51"/>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="51"/>
+      <c r="R19" s="51"/>
+      <c r="S19" s="51"/>
+      <c r="T19" s="51"/>
+      <c r="U19" s="52"/>
     </row>
     <row r="20" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="24">
@@ -5619,20 +5619,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="37" t="s">
+      <c r="J20" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="38"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="39"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="52"/>
     </row>
     <row r="21" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="24">
@@ -5664,20 +5664,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="37" t="s">
+      <c r="J21" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="39"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="51"/>
+      <c r="R21" s="51"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="52"/>
     </row>
     <row r="22" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="20">
@@ -5709,20 +5709,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="34" t="s">
+      <c r="J22" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="36"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="57"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="57"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="58"/>
     </row>
     <row r="23" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="24">
@@ -5754,20 +5754,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="37" t="s">
+      <c r="J23" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="39"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="51"/>
+      <c r="R23" s="51"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
+      <c r="U23" s="52"/>
     </row>
     <row r="24" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
@@ -5889,20 +5889,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J26" s="34" t="s">
+      <c r="J26" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="36"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="57"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="57"/>
+      <c r="U26" s="58"/>
     </row>
     <row r="27" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
@@ -6020,20 +6020,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="37" t="s">
+      <c r="J29" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="38"/>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="39"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="51"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="51"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="51"/>
+      <c r="R29" s="51"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="51"/>
+      <c r="U29" s="52"/>
     </row>
     <row r="30" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
@@ -6110,20 +6110,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="34" t="s">
+      <c r="J31" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="36"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="58"/>
     </row>
     <row r="32" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="20">
@@ -6154,20 +6154,20 @@
       <c r="I32" s="20">
         <v>0</v>
       </c>
-      <c r="J32" s="34" t="s">
+      <c r="J32" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35"/>
-      <c r="S32" s="35"/>
-      <c r="T32" s="35"/>
-      <c r="U32" s="36"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="57"/>
+      <c r="O32" s="57"/>
+      <c r="P32" s="57"/>
+      <c r="Q32" s="57"/>
+      <c r="R32" s="57"/>
+      <c r="S32" s="57"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="58"/>
     </row>
     <row r="33" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
@@ -6199,20 +6199,20 @@
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="J33" s="31" t="s">
+      <c r="J33" s="53" t="s">
         <v>323</v>
       </c>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="32"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="32"/>
-      <c r="T33" s="32"/>
-      <c r="U33" s="33"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="54"/>
+      <c r="N33" s="54"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="54"/>
+      <c r="Q33" s="54"/>
+      <c r="R33" s="54"/>
+      <c r="S33" s="54"/>
+      <c r="T33" s="54"/>
+      <c r="U33" s="55"/>
     </row>
     <row r="34" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
@@ -6287,20 +6287,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J35" s="34" t="s">
+      <c r="J35" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="K35" s="35"/>
-      <c r="L35" s="35"/>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="35"/>
-      <c r="Q35" s="35"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-      <c r="U35" s="36"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="57"/>
+      <c r="O35" s="57"/>
+      <c r="P35" s="57"/>
+      <c r="Q35" s="57"/>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="58"/>
     </row>
     <row r="36" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
@@ -6377,20 +6377,20 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J37" s="34" t="s">
+      <c r="J37" s="56" t="s">
         <v>330</v>
       </c>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="35"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="35"/>
-      <c r="S37" s="35"/>
-      <c r="T37" s="35"/>
-      <c r="U37" s="36"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="58"/>
     </row>
     <row r="38" spans="1:21" ht="15" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
@@ -6572,12 +6572,27 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J8:U8"/>
-    <mergeCell ref="A1:U3"/>
-    <mergeCell ref="J4:U4"/>
-    <mergeCell ref="J5:U5"/>
-    <mergeCell ref="J6:U6"/>
-    <mergeCell ref="J7:U7"/>
+    <mergeCell ref="J39:U39"/>
+    <mergeCell ref="J40:U40"/>
+    <mergeCell ref="J41:U41"/>
+    <mergeCell ref="J33:U33"/>
+    <mergeCell ref="J34:U34"/>
+    <mergeCell ref="J35:U35"/>
+    <mergeCell ref="J36:U36"/>
+    <mergeCell ref="J37:U37"/>
+    <mergeCell ref="J38:U38"/>
+    <mergeCell ref="J32:U32"/>
+    <mergeCell ref="J21:U21"/>
+    <mergeCell ref="J22:U22"/>
+    <mergeCell ref="J23:U23"/>
+    <mergeCell ref="J24:U24"/>
+    <mergeCell ref="J25:U25"/>
+    <mergeCell ref="J26:U26"/>
+    <mergeCell ref="J27:U27"/>
+    <mergeCell ref="J28:U28"/>
+    <mergeCell ref="J29:U29"/>
+    <mergeCell ref="J30:U30"/>
+    <mergeCell ref="J31:U31"/>
     <mergeCell ref="J20:U20"/>
     <mergeCell ref="J9:U9"/>
     <mergeCell ref="J10:U10"/>
@@ -6590,27 +6605,12 @@
     <mergeCell ref="J17:U17"/>
     <mergeCell ref="J18:U18"/>
     <mergeCell ref="J19:U19"/>
-    <mergeCell ref="J32:U32"/>
-    <mergeCell ref="J21:U21"/>
-    <mergeCell ref="J22:U22"/>
-    <mergeCell ref="J23:U23"/>
-    <mergeCell ref="J24:U24"/>
-    <mergeCell ref="J25:U25"/>
-    <mergeCell ref="J26:U26"/>
-    <mergeCell ref="J27:U27"/>
-    <mergeCell ref="J28:U28"/>
-    <mergeCell ref="J29:U29"/>
-    <mergeCell ref="J30:U30"/>
-    <mergeCell ref="J31:U31"/>
-    <mergeCell ref="J39:U39"/>
-    <mergeCell ref="J40:U40"/>
-    <mergeCell ref="J41:U41"/>
-    <mergeCell ref="J33:U33"/>
-    <mergeCell ref="J34:U34"/>
-    <mergeCell ref="J35:U35"/>
-    <mergeCell ref="J36:U36"/>
-    <mergeCell ref="J37:U37"/>
-    <mergeCell ref="J38:U38"/>
+    <mergeCell ref="J8:U8"/>
+    <mergeCell ref="A1:U3"/>
+    <mergeCell ref="J4:U4"/>
+    <mergeCell ref="J5:U5"/>
+    <mergeCell ref="J6:U6"/>
+    <mergeCell ref="J7:U7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Grading/Grading assignment.xlsx
+++ b/Grading/Grading assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trank\Downloads\DSA_GR1_Linked_List\Grading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9BA6FF-5A7F-486F-B22E-64B8D6EB80E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14F92E3-F644-4A2E-B1B1-E3E50E57CBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5448" yWindow="1440" windowWidth="14436" windowHeight="9768" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DanhSachSV" sheetId="1" r:id="rId1"/>
@@ -1416,6 +1416,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1423,6 +1442,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1452,43 +1480,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1505,6 +1496,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1847,55 +1847,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="6" width="50.77734375" customWidth="1"/>
-    <col min="7" max="8" width="15.77734375" customWidth="1"/>
-    <col min="9" max="9" width="30.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="50.7109375" customWidth="1"/>
+    <col min="7" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="G1" s="49" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="49"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="G2" s="49" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="G2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="49"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D4" s="49" t="s">
+      <c r="H2" s="28"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D5" s="49" t="s">
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D5" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <f>ROW()-11</f>
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f t="shared" ref="A13:A48" si="0">ROW()-11</f>
         <v>2</v>
@@ -2026,7 +2026,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2056,7 +2056,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2086,7 +2086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2116,7 +2116,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2146,7 +2146,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2176,7 +2176,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2206,7 +2206,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2236,7 +2236,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2266,7 +2266,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2296,7 +2296,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2326,7 +2326,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2356,7 +2356,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2386,7 +2386,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2416,7 +2416,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2446,7 +2446,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2476,7 +2476,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2506,7 +2506,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2536,7 +2536,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2566,7 +2566,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2596,7 +2596,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2626,7 +2626,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2656,7 +2656,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2686,7 +2686,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2716,7 +2716,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2746,7 +2746,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2776,7 +2776,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2806,7 +2806,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2836,7 +2836,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2866,7 +2866,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2896,7 +2896,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2926,7 +2926,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2956,7 +2956,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2986,7 +2986,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3016,7 +3016,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3046,7 +3046,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3095,88 +3095,88 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CC21D2-106A-4417-8660-7E8FD2EA5170}">
   <dimension ref="A1:T41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="7" width="11.77734375" customWidth="1"/>
-    <col min="8" max="8" width="15.77734375" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" customWidth="1"/>
-    <col min="20" max="20" width="29.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" customWidth="1"/>
+    <col min="20" max="20" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="33"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="36"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="37"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="39"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="43"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="46"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="49"/>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>244</v>
       </c>
@@ -3201,22 +3201,22 @@
       <c r="H4" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="48"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="34"/>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>ROW()-4</f>
         <v>1</v>
@@ -3243,22 +3243,22 @@
         <f>SUM(D5:G5)</f>
         <v>7.75</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="30"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="37"/>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f t="shared" ref="A6:A41" si="0">ROW()-4</f>
         <v>2</v>
@@ -3285,22 +3285,22 @@
         <f t="shared" ref="H6:H41" si="1">SUM(D6:G6)</f>
         <v>9.6</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="30"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="37"/>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3327,22 +3327,22 @@
         <f t="shared" si="1"/>
         <v>9.85</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="30"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="37"/>
+    </row>
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3369,22 +3369,22 @@
         <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="30"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="37"/>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3411,22 +3411,22 @@
         <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="30"/>
-    </row>
-    <row r="10" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="37"/>
+    </row>
+    <row r="10" spans="1:20" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3453,22 +3453,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="I10" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="42"/>
-    </row>
-    <row r="11" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="31"/>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3495,22 +3495,22 @@
         <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="I11" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="30"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="37"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3537,22 +3537,22 @@
         <f t="shared" si="1"/>
         <v>8.25</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="35" t="s">
         <v>307</v>
       </c>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="30"/>
-    </row>
-    <row r="13" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="37"/>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3579,22 +3579,22 @@
         <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="I13" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="30"/>
-    </row>
-    <row r="14" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="37"/>
+    </row>
+    <row r="14" spans="1:20" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3621,22 +3621,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="42"/>
-    </row>
-    <row r="15" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="31"/>
+    </row>
+    <row r="15" spans="1:20" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3662,22 +3662,22 @@
       <c r="H15" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I15" s="43" t="s">
+      <c r="I15" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="44"/>
-      <c r="S15" s="44"/>
-      <c r="T15" s="45"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="40"/>
+    </row>
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3704,22 +3704,22 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="30"/>
-    </row>
-    <row r="17" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="37"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3746,22 +3746,22 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="30"/>
-    </row>
-    <row r="18" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
+      <c r="T17" s="37"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3788,22 +3788,22 @@
         <f t="shared" si="1"/>
         <v>6.6</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="30"/>
-    </row>
-    <row r="19" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="37"/>
+    </row>
+    <row r="19" spans="1:20" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3829,22 +3829,22 @@
       <c r="H19" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="45"/>
-    </row>
-    <row r="20" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="39"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="40"/>
+    </row>
+    <row r="20" spans="1:20" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3870,22 +3870,22 @@
       <c r="H20" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I20" s="43" t="s">
+      <c r="I20" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="44"/>
-      <c r="T20" s="45"/>
-    </row>
-    <row r="21" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="39"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="40"/>
+    </row>
+    <row r="21" spans="1:20" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3911,22 +3911,22 @@
       <c r="H21" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I21" s="43" t="s">
+      <c r="I21" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="44"/>
-      <c r="T21" s="45"/>
-    </row>
-    <row r="22" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="40"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3953,22 +3953,22 @@
         <f t="shared" si="1"/>
         <v>9.35</v>
       </c>
-      <c r="I22" s="28" t="s">
+      <c r="I22" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="30"/>
-    </row>
-    <row r="23" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="37"/>
+    </row>
+    <row r="23" spans="1:20" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3994,22 +3994,22 @@
       <c r="H23" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I23" s="43" t="s">
+      <c r="I23" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="44"/>
-      <c r="S23" s="44"/>
-      <c r="T23" s="45"/>
-    </row>
-    <row r="24" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="40"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -4036,22 +4036,22 @@
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="I24" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="30"/>
-    </row>
-    <row r="25" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="37"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -4078,22 +4078,22 @@
         <f t="shared" si="1"/>
         <v>9.85</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="30"/>
-    </row>
-    <row r="26" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="36"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="37"/>
+    </row>
+    <row r="26" spans="1:20" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -4120,22 +4120,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="40" t="s">
+      <c r="I26" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="41"/>
-      <c r="S26" s="41"/>
-      <c r="T26" s="42"/>
-    </row>
-    <row r="27" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -4162,22 +4162,22 @@
         <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="30"/>
-    </row>
-    <row r="28" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="37"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <f>ROW()-4</f>
         <v>24</v>
@@ -4204,22 +4204,22 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I28" s="28" t="s">
+      <c r="I28" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="30"/>
-    </row>
-    <row r="29" spans="1:20" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="36"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="37"/>
+    </row>
+    <row r="29" spans="1:20" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -4245,22 +4245,22 @@
       <c r="H29" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="I29" s="43" t="s">
+      <c r="I29" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
-      <c r="T29" s="45"/>
-    </row>
-    <row r="30" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="39"/>
+      <c r="T29" s="40"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -4287,22 +4287,22 @@
         <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
-      <c r="I30" s="28" t="s">
+      <c r="I30" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="30"/>
-    </row>
-    <row r="31" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="36"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="37"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -4329,22 +4329,22 @@
         <f t="shared" si="1"/>
         <v>7.85</v>
       </c>
-      <c r="I31" s="28" t="s">
+      <c r="I31" s="35" t="s">
         <v>296</v>
       </c>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="29"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="29"/>
-      <c r="S31" s="29"/>
-      <c r="T31" s="30"/>
-    </row>
-    <row r="32" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="36"/>
+      <c r="T31" s="37"/>
+    </row>
+    <row r="32" spans="1:20" s="13" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <f>ROW()-4</f>
         <v>28</v>
@@ -4371,22 +4371,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I32" s="40" t="s">
+      <c r="I32" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
-      <c r="M32" s="41"/>
-      <c r="N32" s="41"/>
-      <c r="O32" s="41"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="41"/>
-      <c r="S32" s="41"/>
-      <c r="T32" s="42"/>
-    </row>
-    <row r="33" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="31"/>
+    </row>
+    <row r="33" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -4413,22 +4413,22 @@
         <f t="shared" si="1"/>
         <v>8.85</v>
       </c>
-      <c r="I33" s="28" t="s">
+      <c r="I33" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="J33" s="29"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="29"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29"/>
-      <c r="T33" s="30"/>
-    </row>
-    <row r="34" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="36"/>
+      <c r="P33" s="36"/>
+      <c r="Q33" s="36"/>
+      <c r="R33" s="36"/>
+      <c r="S33" s="36"/>
+      <c r="T33" s="37"/>
+    </row>
+    <row r="34" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -4455,22 +4455,22 @@
         <f t="shared" si="1"/>
         <v>9.85</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="29"/>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="29"/>
-      <c r="S34" s="29"/>
-      <c r="T34" s="30"/>
-    </row>
-    <row r="35" spans="1:20" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="37"/>
+    </row>
+    <row r="35" spans="1:20" s="13" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -4497,22 +4497,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="40" t="s">
+      <c r="I35" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="41"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="41"/>
-      <c r="T35" s="42"/>
-    </row>
-    <row r="36" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="S35" s="30"/>
+      <c r="T35" s="31"/>
+    </row>
+    <row r="36" spans="1:20" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <f>ROW()-4</f>
         <v>32</v>
@@ -4539,22 +4539,22 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="I36" s="28" t="s">
+      <c r="I36" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="J36" s="29"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="30"/>
-    </row>
-    <row r="37" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="37"/>
+    </row>
+    <row r="37" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -4581,22 +4581,22 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I37" s="28" t="s">
+      <c r="I37" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="30"/>
-    </row>
-    <row r="38" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J37" s="36"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="36"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="36"/>
+      <c r="R37" s="36"/>
+      <c r="S37" s="36"/>
+      <c r="T37" s="37"/>
+    </row>
+    <row r="38" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -4623,22 +4623,22 @@
         <f t="shared" si="1"/>
         <v>9.85</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="I38" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="30"/>
-    </row>
-    <row r="39" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="37"/>
+    </row>
+    <row r="39" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <f>ROW()-4</f>
         <v>35</v>
@@ -4665,22 +4665,22 @@
         <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
-      <c r="I39" s="28" t="s">
+      <c r="I39" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29"/>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29"/>
-      <c r="T39" s="30"/>
-    </row>
-    <row r="40" spans="1:20" ht="30" x14ac:dyDescent="0.3">
+      <c r="J39" s="36"/>
+      <c r="K39" s="36"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36"/>
+      <c r="Q39" s="36"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="37"/>
+    </row>
+    <row r="40" spans="1:20" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -4707,22 +4707,22 @@
         <f t="shared" si="1"/>
         <v>9.75</v>
       </c>
-      <c r="I40" s="28" t="s">
+      <c r="I40" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="30"/>
-    </row>
-    <row r="41" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="37"/>
+    </row>
+    <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -4749,46 +4749,23 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="I41" s="28" t="s">
+      <c r="I41" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="J41" s="29"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="30"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="36"/>
+      <c r="P41" s="36"/>
+      <c r="Q41" s="36"/>
+      <c r="R41" s="36"/>
+      <c r="S41" s="36"/>
+      <c r="T41" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="I14:T14"/>
-    <mergeCell ref="I4:T4"/>
-    <mergeCell ref="I5:T5"/>
-    <mergeCell ref="I6:T6"/>
-    <mergeCell ref="I7:T7"/>
-    <mergeCell ref="I8:T8"/>
-    <mergeCell ref="I9:T9"/>
-    <mergeCell ref="I10:T10"/>
-    <mergeCell ref="I11:T11"/>
-    <mergeCell ref="I12:T12"/>
-    <mergeCell ref="I13:T13"/>
-    <mergeCell ref="I26:T26"/>
-    <mergeCell ref="I15:T15"/>
-    <mergeCell ref="I16:T16"/>
-    <mergeCell ref="I17:T17"/>
-    <mergeCell ref="I18:T18"/>
-    <mergeCell ref="I19:T19"/>
-    <mergeCell ref="I20:T20"/>
-    <mergeCell ref="I21:T21"/>
-    <mergeCell ref="I22:T22"/>
-    <mergeCell ref="I23:T23"/>
-    <mergeCell ref="I24:T24"/>
-    <mergeCell ref="I25:T25"/>
     <mergeCell ref="I39:T39"/>
     <mergeCell ref="I40:T40"/>
     <mergeCell ref="I41:T41"/>
@@ -4805,6 +4782,29 @@
     <mergeCell ref="I30:T30"/>
     <mergeCell ref="I31:T31"/>
     <mergeCell ref="I32:T32"/>
+    <mergeCell ref="I26:T26"/>
+    <mergeCell ref="I15:T15"/>
+    <mergeCell ref="I16:T16"/>
+    <mergeCell ref="I17:T17"/>
+    <mergeCell ref="I18:T18"/>
+    <mergeCell ref="I19:T19"/>
+    <mergeCell ref="I20:T20"/>
+    <mergeCell ref="I21:T21"/>
+    <mergeCell ref="I22:T22"/>
+    <mergeCell ref="I23:T23"/>
+    <mergeCell ref="I24:T24"/>
+    <mergeCell ref="I25:T25"/>
+    <mergeCell ref="I14:T14"/>
+    <mergeCell ref="I4:T4"/>
+    <mergeCell ref="I5:T5"/>
+    <mergeCell ref="I6:T6"/>
+    <mergeCell ref="I7:T7"/>
+    <mergeCell ref="I8:T8"/>
+    <mergeCell ref="I9:T9"/>
+    <mergeCell ref="I10:T10"/>
+    <mergeCell ref="I11:T11"/>
+    <mergeCell ref="I12:T12"/>
+    <mergeCell ref="I13:T13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4813,89 +4813,89 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1BB4D8-6192-4735-A46B-0B72EA33381F}">
   <dimension ref="A1:U41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
     <col min="7" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="33"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="36"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="37"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="39"/>
-    </row>
-    <row r="4" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="43"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="46"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="49"/>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>244</v>
       </c>
@@ -4923,22 +4923,22 @@
       <c r="I4" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="J4" s="46" t="s">
+      <c r="J4" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="48"/>
-    </row>
-    <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="34"/>
+    </row>
+    <row r="5" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <f>ROW()-4</f>
         <v>1</v>
@@ -4968,20 +4968,20 @@
         <f>SUM(D5:H5)</f>
         <v>10</v>
       </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="30"/>
-    </row>
-    <row r="6" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="J5" s="35"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="37"/>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <f t="shared" ref="A6:A41" si="0">ROW()-4</f>
         <v>2</v>
@@ -5011,22 +5011,22 @@
         <f t="shared" ref="I6:I41" si="1">SUM(D6:H6)</f>
         <v>9</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="30"/>
-    </row>
-    <row r="7" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="37"/>
+    </row>
+    <row r="7" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -5056,22 +5056,22 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="30"/>
-    </row>
-    <row r="8" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="37"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5082,29 +5082,39 @@
       <c r="C8" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5">
+        <v>2</v>
+      </c>
       <c r="I8" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="30"/>
-    </row>
-    <row r="9" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="J8" s="35"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="37"/>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -5134,22 +5144,22 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="30"/>
-    </row>
-    <row r="10" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="37"/>
+    </row>
+    <row r="10" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5179,22 +5189,22 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J10" s="53" t="s">
+      <c r="J10" s="50" t="s">
         <v>318</v>
       </c>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="55"/>
-    </row>
-    <row r="11" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="51"/>
+      <c r="U10" s="52"/>
+    </row>
+    <row r="11" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5224,20 +5234,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="30"/>
-    </row>
-    <row r="12" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J11" s="35"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="37"/>
+    </row>
+    <row r="12" spans="1:21" s="23" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5267,22 +5277,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="56" t="s">
+      <c r="J12" s="53" t="s">
         <v>330</v>
       </c>
-      <c r="K12" s="57"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="57"/>
-      <c r="O12" s="57"/>
-      <c r="P12" s="57"/>
-      <c r="Q12" s="57"/>
-      <c r="R12" s="57"/>
-      <c r="S12" s="57"/>
-      <c r="T12" s="57"/>
-      <c r="U12" s="58"/>
-    </row>
-    <row r="13" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="55"/>
+    </row>
+    <row r="13" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5312,20 +5322,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="30"/>
-    </row>
-    <row r="14" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J13" s="35"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="37"/>
+    </row>
+    <row r="14" spans="1:21" s="23" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -5355,22 +5365,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="56" t="s">
+      <c r="J14" s="53" t="s">
         <v>330</v>
       </c>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="57"/>
-      <c r="P14" s="57"/>
-      <c r="Q14" s="57"/>
-      <c r="R14" s="57"/>
-      <c r="S14" s="57"/>
-      <c r="T14" s="57"/>
-      <c r="U14" s="58"/>
-    </row>
-    <row r="15" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K14" s="54"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="54"/>
+      <c r="U14" s="55"/>
+    </row>
+    <row r="15" spans="1:21" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -5400,22 +5410,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="50" t="s">
+      <c r="J15" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="K15" s="51"/>
-      <c r="L15" s="51"/>
-      <c r="M15" s="51"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="51"/>
-      <c r="S15" s="51"/>
-      <c r="T15" s="51"/>
-      <c r="U15" s="52"/>
-    </row>
-    <row r="16" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="58"/>
+    </row>
+    <row r="16" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -5445,20 +5455,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="30"/>
-    </row>
-    <row r="17" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="J16" s="35"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
+      <c r="S16" s="36"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="37"/>
+    </row>
+    <row r="17" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -5488,20 +5498,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J17" s="28"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="29"/>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="30"/>
-    </row>
-    <row r="18" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="J17" s="35"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="37"/>
+    </row>
+    <row r="18" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -5531,20 +5541,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J18" s="28"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="29"/>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="30"/>
-    </row>
-    <row r="19" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J18" s="35"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="37"/>
+    </row>
+    <row r="19" spans="1:21" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -5574,22 +5584,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="50" t="s">
+      <c r="J19" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="K19" s="51"/>
-      <c r="L19" s="51"/>
-      <c r="M19" s="51"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="51"/>
-      <c r="S19" s="51"/>
-      <c r="T19" s="51"/>
-      <c r="U19" s="52"/>
-    </row>
-    <row r="20" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="58"/>
+    </row>
+    <row r="20" spans="1:21" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -5619,22 +5629,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="50" t="s">
+      <c r="J20" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="51"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="52"/>
-    </row>
-    <row r="21" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="58"/>
+    </row>
+    <row r="21" spans="1:21" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="24">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -5664,22 +5674,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="50" t="s">
+      <c r="J21" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="52"/>
-    </row>
-    <row r="22" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="58"/>
+    </row>
+    <row r="22" spans="1:21" s="23" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -5709,22 +5719,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="56" t="s">
+      <c r="J22" s="53" t="s">
         <v>330</v>
       </c>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="57"/>
-      <c r="P22" s="57"/>
-      <c r="Q22" s="57"/>
-      <c r="R22" s="57"/>
-      <c r="S22" s="57"/>
-      <c r="T22" s="57"/>
-      <c r="U22" s="58"/>
-    </row>
-    <row r="23" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="55"/>
+    </row>
+    <row r="23" spans="1:21" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="24">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -5754,22 +5764,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="50" t="s">
+      <c r="J23" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="K23" s="51"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="51"/>
-      <c r="R23" s="51"/>
-      <c r="S23" s="51"/>
-      <c r="T23" s="51"/>
-      <c r="U23" s="52"/>
-    </row>
-    <row r="24" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="57"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="57"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="58"/>
+    </row>
+    <row r="24" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -5799,22 +5809,22 @@
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="J24" s="28" t="s">
+      <c r="J24" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="30"/>
-    </row>
-    <row r="25" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="37"/>
+    </row>
+    <row r="25" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5844,22 +5854,22 @@
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
-      <c r="J25" s="28" t="s">
+      <c r="J25" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="30"/>
-    </row>
-    <row r="26" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="36"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="37"/>
+    </row>
+    <row r="26" spans="1:21" s="23" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="20">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -5889,22 +5899,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J26" s="56" t="s">
+      <c r="J26" s="53" t="s">
         <v>330</v>
       </c>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="57"/>
-      <c r="R26" s="57"/>
-      <c r="S26" s="57"/>
-      <c r="T26" s="57"/>
-      <c r="U26" s="58"/>
-    </row>
-    <row r="27" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
+      <c r="R26" s="54"/>
+      <c r="S26" s="54"/>
+      <c r="T26" s="54"/>
+      <c r="U26" s="55"/>
+    </row>
+    <row r="27" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -5934,20 +5944,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J27" s="28"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="30"/>
-    </row>
-    <row r="28" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="J27" s="35"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="37"/>
+    </row>
+    <row r="28" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <f>ROW()-4</f>
         <v>24</v>
@@ -5977,20 +5987,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="30"/>
-    </row>
-    <row r="29" spans="1:21" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J28" s="35"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="36"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="37"/>
+    </row>
+    <row r="29" spans="1:21" s="27" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="24">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6020,22 +6030,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="50" t="s">
+      <c r="J29" s="56" t="s">
         <v>293</v>
       </c>
-      <c r="K29" s="51"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51"/>
-      <c r="U29" s="52"/>
-    </row>
-    <row r="30" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="57"/>
+      <c r="S29" s="57"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="58"/>
+    </row>
+    <row r="30" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -6065,22 +6075,22 @@
         <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
-      <c r="J30" s="28" t="s">
+      <c r="J30" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="30"/>
-    </row>
-    <row r="31" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="36"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="37"/>
+    </row>
+    <row r="31" spans="1:21" s="23" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="20">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -6110,22 +6120,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="56" t="s">
+      <c r="J31" s="53" t="s">
         <v>330</v>
       </c>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="57"/>
-      <c r="N31" s="57"/>
-      <c r="O31" s="57"/>
-      <c r="P31" s="57"/>
-      <c r="Q31" s="57"/>
-      <c r="R31" s="57"/>
-      <c r="S31" s="57"/>
-      <c r="T31" s="57"/>
-      <c r="U31" s="58"/>
-    </row>
-    <row r="32" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K31" s="54"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="54"/>
+      <c r="N31" s="54"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="54"/>
+      <c r="Q31" s="54"/>
+      <c r="R31" s="54"/>
+      <c r="S31" s="54"/>
+      <c r="T31" s="54"/>
+      <c r="U31" s="55"/>
+    </row>
+    <row r="32" spans="1:21" s="23" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="20">
         <f>ROW()-4</f>
         <v>28</v>
@@ -6154,22 +6164,22 @@
       <c r="I32" s="20">
         <v>0</v>
       </c>
-      <c r="J32" s="56" t="s">
+      <c r="J32" s="53" t="s">
         <v>330</v>
       </c>
-      <c r="K32" s="57"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="57"/>
-      <c r="N32" s="57"/>
-      <c r="O32" s="57"/>
-      <c r="P32" s="57"/>
-      <c r="Q32" s="57"/>
-      <c r="R32" s="57"/>
-      <c r="S32" s="57"/>
-      <c r="T32" s="57"/>
-      <c r="U32" s="58"/>
-    </row>
-    <row r="33" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K32" s="54"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="54"/>
+      <c r="N32" s="54"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="54"/>
+      <c r="R32" s="54"/>
+      <c r="S32" s="54"/>
+      <c r="T32" s="54"/>
+      <c r="U32" s="55"/>
+    </row>
+    <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6199,22 +6209,22 @@
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="J33" s="53" t="s">
+      <c r="J33" s="50" t="s">
         <v>323</v>
       </c>
-      <c r="K33" s="54"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="54"/>
-      <c r="N33" s="54"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="54"/>
-      <c r="Q33" s="54"/>
-      <c r="R33" s="54"/>
-      <c r="S33" s="54"/>
-      <c r="T33" s="54"/>
-      <c r="U33" s="55"/>
-    </row>
-    <row r="34" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K33" s="51"/>
+      <c r="L33" s="51"/>
+      <c r="M33" s="51"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="51"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="51"/>
+      <c r="R33" s="51"/>
+      <c r="S33" s="51"/>
+      <c r="T33" s="51"/>
+      <c r="U33" s="52"/>
+    </row>
+    <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6244,20 +6254,20 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J34" s="28"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="29"/>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
-      <c r="R34" s="29"/>
-      <c r="S34" s="29"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="30"/>
-    </row>
-    <row r="35" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="J34" s="35"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="37"/>
+    </row>
+    <row r="35" spans="1:21" s="23" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="20">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -6287,22 +6297,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J35" s="56" t="s">
+      <c r="J35" s="53" t="s">
         <v>330</v>
       </c>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="57"/>
-      <c r="N35" s="57"/>
-      <c r="O35" s="57"/>
-      <c r="P35" s="57"/>
-      <c r="Q35" s="57"/>
-      <c r="R35" s="57"/>
-      <c r="S35" s="57"/>
-      <c r="T35" s="57"/>
-      <c r="U35" s="58"/>
-    </row>
-    <row r="36" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
+    </row>
+    <row r="36" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <f>ROW()-4</f>
         <v>32</v>
@@ -6332,22 +6342,22 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="J36" s="28" t="s">
+      <c r="J36" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="30"/>
-    </row>
-    <row r="37" spans="1:21" s="23" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="37"/>
+    </row>
+    <row r="37" spans="1:21" s="23" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="20">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -6377,22 +6387,22 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J37" s="56" t="s">
+      <c r="J37" s="53" t="s">
         <v>330</v>
       </c>
-      <c r="K37" s="57"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="57"/>
-      <c r="N37" s="57"/>
-      <c r="O37" s="57"/>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="58"/>
-    </row>
-    <row r="38" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K37" s="54"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="54"/>
+      <c r="N37" s="54"/>
+      <c r="O37" s="54"/>
+      <c r="P37" s="54"/>
+      <c r="Q37" s="54"/>
+      <c r="R37" s="54"/>
+      <c r="S37" s="54"/>
+      <c r="T37" s="54"/>
+      <c r="U37" s="55"/>
+    </row>
+    <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -6422,22 +6432,22 @@
         <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
-      <c r="J38" s="28" t="s">
+      <c r="J38" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="30"/>
-    </row>
-    <row r="39" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K38" s="36"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="37"/>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <f>ROW()-4</f>
         <v>35</v>
@@ -6467,22 +6477,22 @@
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="J39" s="28" t="s">
+      <c r="J39" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29"/>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29"/>
-      <c r="T39" s="29"/>
-      <c r="U39" s="30"/>
-    </row>
-    <row r="40" spans="1:21" ht="30" x14ac:dyDescent="0.3">
+      <c r="K39" s="36"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36"/>
+      <c r="Q39" s="36"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="37"/>
+    </row>
+    <row r="40" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -6512,22 +6522,22 @@
         <f t="shared" si="1"/>
         <v>5.5</v>
       </c>
-      <c r="J40" s="28" t="s">
+      <c r="J40" s="35" t="s">
         <v>328</v>
       </c>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="30"/>
-    </row>
-    <row r="41" spans="1:21" ht="15" x14ac:dyDescent="0.3">
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+      <c r="U40" s="37"/>
+    </row>
+    <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -6557,30 +6567,39 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="J41" s="28"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="30"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="36"/>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="36"/>
+      <c r="P41" s="36"/>
+      <c r="Q41" s="36"/>
+      <c r="R41" s="36"/>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+      <c r="U41" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J39:U39"/>
-    <mergeCell ref="J40:U40"/>
-    <mergeCell ref="J41:U41"/>
-    <mergeCell ref="J33:U33"/>
-    <mergeCell ref="J34:U34"/>
-    <mergeCell ref="J35:U35"/>
-    <mergeCell ref="J36:U36"/>
-    <mergeCell ref="J37:U37"/>
-    <mergeCell ref="J38:U38"/>
+    <mergeCell ref="J8:U8"/>
+    <mergeCell ref="A1:U3"/>
+    <mergeCell ref="J4:U4"/>
+    <mergeCell ref="J5:U5"/>
+    <mergeCell ref="J6:U6"/>
+    <mergeCell ref="J7:U7"/>
+    <mergeCell ref="J20:U20"/>
+    <mergeCell ref="J9:U9"/>
+    <mergeCell ref="J10:U10"/>
+    <mergeCell ref="J11:U11"/>
+    <mergeCell ref="J12:U12"/>
+    <mergeCell ref="J13:U13"/>
+    <mergeCell ref="J14:U14"/>
+    <mergeCell ref="J15:U15"/>
+    <mergeCell ref="J16:U16"/>
+    <mergeCell ref="J17:U17"/>
+    <mergeCell ref="J18:U18"/>
+    <mergeCell ref="J19:U19"/>
     <mergeCell ref="J32:U32"/>
     <mergeCell ref="J21:U21"/>
     <mergeCell ref="J22:U22"/>
@@ -6593,24 +6612,15 @@
     <mergeCell ref="J29:U29"/>
     <mergeCell ref="J30:U30"/>
     <mergeCell ref="J31:U31"/>
-    <mergeCell ref="J20:U20"/>
-    <mergeCell ref="J9:U9"/>
-    <mergeCell ref="J10:U10"/>
-    <mergeCell ref="J11:U11"/>
-    <mergeCell ref="J12:U12"/>
-    <mergeCell ref="J13:U13"/>
-    <mergeCell ref="J14:U14"/>
-    <mergeCell ref="J15:U15"/>
-    <mergeCell ref="J16:U16"/>
-    <mergeCell ref="J17:U17"/>
-    <mergeCell ref="J18:U18"/>
-    <mergeCell ref="J19:U19"/>
-    <mergeCell ref="J8:U8"/>
-    <mergeCell ref="A1:U3"/>
-    <mergeCell ref="J4:U4"/>
-    <mergeCell ref="J5:U5"/>
-    <mergeCell ref="J6:U6"/>
-    <mergeCell ref="J7:U7"/>
+    <mergeCell ref="J39:U39"/>
+    <mergeCell ref="J40:U40"/>
+    <mergeCell ref="J41:U41"/>
+    <mergeCell ref="J33:U33"/>
+    <mergeCell ref="J34:U34"/>
+    <mergeCell ref="J35:U35"/>
+    <mergeCell ref="J36:U36"/>
+    <mergeCell ref="J37:U37"/>
+    <mergeCell ref="J38:U38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
